--- a/public/templates/plantilla-inmuebles-atlas.xlsx
+++ b/public/templates/plantilla-inmuebles-atlas.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Atlas" sheetId="1" r:id="rId1"/>
+    <sheet name="Léeme" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -32,8 +33,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,8 +66,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:U2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,34 +410,61 @@
         <v>Dirección</v>
       </c>
       <c r="C1" t="str">
+        <v>Tipo de inmueble (piso/parking/trastero/local/otro)</v>
+      </c>
+      <c r="D1" t="str">
         <v>Referencia catastral</v>
       </c>
-      <c r="D1" t="str">
-        <v>Modo explotación (completo/habitaciones)</v>
-      </c>
       <c r="E1" t="str">
+        <v>Uso y alquiler (larga_estancia/temporada/turistico/mixto/vivienda_habitual/disponible)</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Alquiler por habitaciones (sí/no)</v>
+      </c>
+      <c r="G1" t="str">
         <v>Nº habitaciones</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
+        <v>Baños</v>
+      </c>
+      <c r="I1" t="str">
+        <v>m² útiles</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Urbana/rústica</v>
+      </c>
+      <c r="K1" t="str">
+        <v>% propiedad</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Anexo parking (sí/no)</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Anexo trastero (sí/no)</v>
+      </c>
+      <c r="N1" t="str">
         <v>Fecha compra</v>
       </c>
-      <c r="G1" t="str">
+      <c r="O1" t="str">
         <v>Precio compra €</v>
       </c>
-      <c r="H1" t="str">
+      <c r="P1" t="str">
         <v>Gastos compra €</v>
       </c>
-      <c r="I1" t="str">
+      <c r="Q1" t="str">
         <v>Aportación propia €</v>
       </c>
-      <c r="J1" t="str">
+      <c r="R1" t="str">
         <v>Importe financiado €</v>
       </c>
-      <c r="K1" t="str">
+      <c r="S1" t="str">
         <v>Valor catastral €</v>
       </c>
-      <c r="L1" t="str">
+      <c r="T1" t="str">
         <v>Valor catastral construcción €</v>
+      </c>
+      <c r="U1" t="str">
+        <v>Valor catastral revisado (sí/no)</v>
       </c>
     </row>
     <row r="2">
@@ -445,39 +475,127 @@
         <v>Calle Mayor 10, Madrid</v>
       </c>
       <c r="C2" t="str">
+        <v>piso</v>
+      </c>
+      <c r="D2" t="str">
         <v>1234567VK1234S0001AB</v>
       </c>
-      <c r="D2" t="str">
-        <v>completo</v>
-      </c>
       <c r="E2" t="str">
-        <v/>
+        <v>larga_estancia</v>
       </c>
       <c r="F2" t="str">
-        <v>2021-06-15</v>
+        <v>no</v>
       </c>
       <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>90</v>
+      </c>
+      <c r="J2" t="str">
+        <v>urbana</v>
+      </c>
+      <c r="K2">
+        <v>100</v>
+      </c>
+      <c r="L2" t="str">
+        <v>sí</v>
+      </c>
+      <c r="M2" t="str">
+        <v>no</v>
+      </c>
+      <c r="N2" s="1">
+        <v>44362</v>
+      </c>
+      <c r="O2">
         <v>100000</v>
       </c>
-      <c r="H2">
+      <c r="P2">
         <v>12000</v>
       </c>
-      <c r="I2">
+      <c r="Q2">
         <v>32000</v>
       </c>
-      <c r="J2">
+      <c r="R2">
         <v>80000</v>
       </c>
-      <c r="K2">
+      <c r="S2">
         <v>60000</v>
       </c>
-      <c r="L2">
+      <c r="T2">
         <v>42000</v>
+      </c>
+      <c r="U2" t="str">
+        <v>sí</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PLANTILLA DE INMUEBLES · Atlas</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Obligatorias: Alias o Dirección, y Tipo de inmueble. El resto es opcional;</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>lo que dejes vacío lo podrás completar luego en la ficha del inmueble.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>NO se incluyen aquí (se editan en la ficha del inmueble, son listas):</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v xml:space="preserve"> · Mejoras / reformas previas</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v xml:space="preserve"> · Mobiliario</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Fechas en formato DD/MM/AAAA. Importes con coma decimal (1.234,56).</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A10"/>
   </ignoredErrors>
 </worksheet>
 </file>